--- a/apps/deep/www/calculators/mn-sqt-adapted.xlsx
+++ b/apps/deep/www/calculators/mn-sqt-adapted.xlsx
@@ -1522,7 +1522,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -1655,7 +1655,7 @@
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -2665,7 +2665,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -5377,7 +5377,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -5421,7 +5421,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9585,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -9619,7 +9619,7 @@
     <row r="2" ht="21" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -10203,7 +10203,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
